--- a/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.146</v>
+        <v>0.114</v>
       </c>
       <c r="E2">
-        <v>0.165</v>
+        <v>0.07205</v>
       </c>
       <c r="F2">
-        <v>0.22</v>
+        <v>0.326</v>
       </c>
       <c r="G2">
-        <v>0.05446459801129266</v>
+        <v>0.02768728746985437</v>
       </c>
       <c r="H2">
-        <v>0.05446459801129266</v>
+        <v>0.02762869003605574</v>
       </c>
       <c r="I2">
-        <v>0.1135928313263046</v>
+        <v>0.07031692055836032</v>
       </c>
       <c r="J2">
-        <v>0.09753945389623543</v>
+        <v>0.06250627467817614</v>
       </c>
       <c r="K2">
-        <v>92.03999999999999</v>
+        <v>49.72</v>
       </c>
       <c r="L2">
-        <v>0.1533003547693999</v>
+        <v>0.09104576276462693</v>
       </c>
       <c r="M2">
-        <v>10.60238</v>
+        <v>43.40051</v>
       </c>
       <c r="N2">
-        <v>0.01225708670520231</v>
+        <v>0.06200072857142858</v>
       </c>
       <c r="O2">
-        <v>0.1151931768796176</v>
+        <v>0.872898431214803</v>
       </c>
       <c r="P2">
-        <v>10.60238</v>
+        <v>27.80051</v>
       </c>
       <c r="Q2">
-        <v>0.01225708670520231</v>
+        <v>0.03971501428571429</v>
       </c>
       <c r="R2">
-        <v>0.1151931768796176</v>
+        <v>0.5591413917940468</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.3594427807415166</v>
       </c>
       <c r="U2">
-        <v>92.211</v>
+        <v>185.319</v>
       </c>
       <c r="V2">
-        <v>0.1066023121387283</v>
+        <v>0.2647414285714286</v>
       </c>
       <c r="W2">
-        <v>0.1003335456137558</v>
+        <v>0.0614050303555941</v>
       </c>
       <c r="X2">
-        <v>0.04290246962067951</v>
+        <v>0.07085998110466979</v>
       </c>
       <c r="Y2">
-        <v>0.05743107599307626</v>
+        <v>-0.009454950749075687</v>
       </c>
       <c r="Z2">
-        <v>0.1663816460584435</v>
+        <v>0.1419173244962068</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02408685342056918</v>
+        <v>0.04817081295099274</v>
       </c>
       <c r="AC2">
-        <v>-0.02401113801943956</v>
+        <v>-0.04817081295099274</v>
       </c>
       <c r="AD2">
-        <v>2509.138</v>
+        <v>2320.489</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2509.138</v>
+        <v>2320.489</v>
       </c>
       <c r="AG2">
-        <v>2416.927000000001</v>
+        <v>2135.17</v>
       </c>
       <c r="AH2">
-        <v>0.7436382270079055</v>
+        <v>0.768249445702335</v>
       </c>
       <c r="AI2">
-        <v>0.6509906500156447</v>
+        <v>0.653274453427265</v>
       </c>
       <c r="AJ2">
-        <v>0.7364353320473003</v>
+        <v>0.7531012249706367</v>
       </c>
       <c r="AK2">
-        <v>0.6424363132876695</v>
+        <v>0.6341894456704794</v>
       </c>
       <c r="AL2">
-        <v>70.5</v>
+        <v>57.563</v>
       </c>
       <c r="AM2">
-        <v>70.265</v>
+        <v>56.998</v>
       </c>
       <c r="AN2">
-        <v>34.51359009628611</v>
+        <v>55.92752645151961</v>
       </c>
       <c r="AO2">
-        <v>0.9673758865248228</v>
+        <v>0.6670951826694232</v>
       </c>
       <c r="AP2">
-        <v>33.24521320495187</v>
+        <v>51.46103974355885</v>
       </c>
       <c r="AQ2">
-        <v>0.9706112573827653</v>
+        <v>0.6737078493982246</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axactor SE (OB:ACR)</t>
+          <t>Axactor ASA (OB:ACR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.61</v>
+        <v>0.247</v>
       </c>
       <c r="F3">
-        <v>0.392</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
-        <v>0.1235827664399093</v>
+        <v>0.09278350515463918</v>
       </c>
       <c r="H3">
-        <v>0.1235827664399093</v>
+        <v>0.09278350515463918</v>
       </c>
       <c r="I3">
-        <v>0.2577475434618292</v>
+        <v>0.2025997310623039</v>
       </c>
       <c r="J3">
-        <v>0.2577475434618292</v>
+        <v>0.2025997310623039</v>
       </c>
       <c r="K3">
-        <v>2.42</v>
+        <v>-7.58</v>
       </c>
       <c r="L3">
-        <v>0.009145880574452002</v>
+        <v>-0.03397579560735096</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,7 +755,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,79 +764,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>45.2</v>
+        <v>17.1</v>
       </c>
       <c r="V3">
-        <v>0.1745847817690228</v>
+        <v>0.09484193011647254</v>
       </c>
       <c r="W3">
-        <v>0.007109283196239718</v>
+        <v>-0.0158477942713778</v>
       </c>
       <c r="X3">
-        <v>0.04535586544891599</v>
+        <v>0.08330100516502151</v>
       </c>
       <c r="Y3">
-        <v>-0.03824658225267627</v>
+        <v>-0.0991487994363993</v>
       </c>
       <c r="Z3">
-        <v>0.1987680288461539</v>
+        <v>0.1692716236722306</v>
       </c>
       <c r="AA3">
-        <v>0.05123197115384617</v>
+        <v>0.03429438543247345</v>
       </c>
       <c r="AB3">
-        <v>0.04211922728947771</v>
+        <v>0.07335195969104118</v>
       </c>
       <c r="AC3">
-        <v>0.009112743864368458</v>
+        <v>-0.03905757425856773</v>
       </c>
       <c r="AD3">
-        <v>949.2</v>
+        <v>870.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>949.2</v>
+        <v>870.8</v>
       </c>
       <c r="AG3">
-        <v>904</v>
+        <v>853.6999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7856965482989819</v>
+        <v>0.8284654171819998</v>
       </c>
       <c r="AI3">
-        <v>0.6603130434782609</v>
+        <v>0.6869674976333229</v>
       </c>
       <c r="AJ3">
-        <v>0.7773669275088141</v>
+        <v>0.8256286266924564</v>
       </c>
       <c r="AK3">
-        <v>0.6492853551677081</v>
+        <v>0.682686925229908</v>
       </c>
       <c r="AL3">
-        <v>70.5</v>
+        <v>57.4</v>
       </c>
       <c r="AM3">
-        <v>70.494</v>
+        <v>57.242</v>
       </c>
       <c r="AN3">
-        <v>13.05639614855571</v>
+        <v>18.52765957446809</v>
       </c>
       <c r="AO3">
-        <v>0.9673758865248228</v>
+        <v>0.7874564459930314</v>
       </c>
       <c r="AP3">
-        <v>12.43466299862448</v>
+        <v>18.16382978723404</v>
       </c>
       <c r="AQ3">
-        <v>0.967458223394899</v>
+        <v>0.7896299919639427</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MyBank ASA (OTCNO:MYBANK)</t>
+          <t>Melhus Sparebank (OB:MELG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,6 +855,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0761</v>
+      </c>
+      <c r="E4">
+        <v>0.0698</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -868,82 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L4">
-        <v>0.372351160443996</v>
+        <v>0.4256521739130434</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>2.68</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.05903083700440529</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2737487231869254</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>2.68</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05903083700440529</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2737487231869254</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>14.5</v>
+        <v>0.399</v>
       </c>
       <c r="V4">
-        <v>0.5686274509803921</v>
+        <v>0.008788546255506608</v>
       </c>
       <c r="W4">
-        <v>0.1911917098445596</v>
+        <v>0.07246484085862324</v>
       </c>
       <c r="X4">
-        <v>0.02309189775075666</v>
+        <v>0.08309737866338221</v>
       </c>
       <c r="Y4">
-        <v>0.1680998120938029</v>
+        <v>-0.01063253780475897</v>
       </c>
       <c r="Z4">
-        <v>1.47910447761194</v>
+        <v>0.05579504297431244</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02311866005481628</v>
+        <v>0.04485768030112966</v>
       </c>
       <c r="AC4">
-        <v>-0.02311866005481628</v>
+        <v>-0.04485768030112966</v>
       </c>
       <c r="AD4">
-        <v>0.638</v>
+        <v>218</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.638</v>
+        <v>218</v>
       </c>
       <c r="AG4">
-        <v>-13.862</v>
+        <v>217.601</v>
       </c>
       <c r="AH4">
-        <v>0.02440890657280588</v>
+        <v>0.8276385725132879</v>
       </c>
       <c r="AI4">
-        <v>0.02537990293579441</v>
+        <v>0.654065406540654</v>
       </c>
       <c r="AJ4">
-        <v>-1.191098126825915</v>
+        <v>0.8273770822164175</v>
       </c>
       <c r="AK4">
-        <v>-1.303064485805603</v>
+        <v>0.6536507850682335</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sunndal Sparebank (OB:SUNSB)</t>
+          <t>Romsdal Sparebank (OB:ROMSB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -968,12 +977,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.124</v>
-      </c>
-      <c r="E5">
-        <v>0.165</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -987,28 +990,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5.06</v>
+        <v>5.62</v>
       </c>
       <c r="L5">
-        <v>0.3953125</v>
+        <v>0.3469135802469136</v>
       </c>
       <c r="M5">
-        <v>1.45168</v>
+        <v>1.44452</v>
       </c>
       <c r="N5">
-        <v>0.04494365325077399</v>
+        <v>0.05471666666666667</v>
       </c>
       <c r="O5">
-        <v>0.286893280632411</v>
+        <v>0.2570320284697509</v>
       </c>
       <c r="P5">
-        <v>1.45168</v>
+        <v>1.44452</v>
       </c>
       <c r="Q5">
-        <v>0.04494365325077399</v>
+        <v>0.05471666666666667</v>
       </c>
       <c r="R5">
-        <v>0.286893280632411</v>
+        <v>0.2570320284697509</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,55 +1020,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.253</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="V5">
-        <v>0.007832817337461301</v>
+        <v>0.3075757575757576</v>
       </c>
       <c r="W5">
-        <v>0.09100719424460431</v>
+        <v>0.06162280701754386</v>
       </c>
       <c r="X5">
-        <v>0.04044907379244302</v>
+        <v>0.0759357472994194</v>
       </c>
       <c r="Y5">
-        <v>0.05055812045216129</v>
+        <v>-0.01431294028187555</v>
       </c>
       <c r="Z5">
-        <v>0.08255028795862168</v>
+        <v>0.0786255096097845</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0239657621354521</v>
+        <v>0.04499700415648328</v>
       </c>
       <c r="AC5">
-        <v>-0.0239657621354521</v>
+        <v>-0.04499700415648328</v>
       </c>
       <c r="AD5">
-        <v>92.5</v>
+        <v>100.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>92.5</v>
+        <v>100.8</v>
       </c>
       <c r="AG5">
-        <v>92.247</v>
+        <v>92.67999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.7411858974358975</v>
+        <v>0.7924528301886793</v>
       </c>
       <c r="AI5">
-        <v>0.5457227138643068</v>
+        <v>0.5656565656565656</v>
       </c>
       <c r="AJ5">
-        <v>0.7406601523922696</v>
+        <v>0.7783003023177696</v>
       </c>
       <c r="AK5">
-        <v>0.545043634451423</v>
+        <v>0.5449200376293509</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tysnes Sparebank (OB:TYSB)</t>
+          <t>Sunndal Sparebank (OB:SUNSB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,6 +1093,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.138</v>
+      </c>
+      <c r="E6">
+        <v>0.192</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1103,82 +1112,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3.27</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
-        <v>0.3682432432432432</v>
+        <v>0.3884892086330936</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.49599</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.05688174904942966</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.2770351851851852</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1.49599</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.05688174904942966</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2770351851851852</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.481</v>
+        <v>10.6</v>
       </c>
       <c r="V6">
-        <v>0.023125</v>
+        <v>0.403041825095057</v>
       </c>
       <c r="W6">
-        <v>0.09909090909090909</v>
+        <v>0.0849056603773585</v>
       </c>
       <c r="X6">
-        <v>0.04845460009837332</v>
+        <v>0.07299609103228802</v>
       </c>
       <c r="Y6">
-        <v>0.05063630899253577</v>
+        <v>0.01190956934507048</v>
       </c>
       <c r="Z6">
-        <v>0.1119882967185411</v>
+        <v>0.08993038482440931</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02405651390342703</v>
+        <v>0.0450721653242823</v>
       </c>
       <c r="AC6">
-        <v>-0.02405651390342703</v>
+        <v>-0.0450721653242823</v>
       </c>
       <c r="AD6">
-        <v>86.8</v>
+        <v>89.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>86.8</v>
+        <v>89.8</v>
       </c>
       <c r="AG6">
-        <v>86.319</v>
+        <v>79.2</v>
       </c>
       <c r="AH6">
-        <v>0.8066914498141264</v>
+        <v>0.7734711455641688</v>
       </c>
       <c r="AI6">
-        <v>0.6651340996168582</v>
+        <v>0.561601000625391</v>
       </c>
       <c r="AJ6">
-        <v>0.8058234300170838</v>
+        <v>0.7507109004739336</v>
       </c>
       <c r="AK6">
-        <v>0.6638952768441535</v>
+        <v>0.5304755525787006</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Melhus Sparebank (OB:MELG)</t>
+          <t>mybank ASA (OTCNO:MYBANK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1203,12 +1215,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0503</v>
-      </c>
-      <c r="E7">
-        <v>0.04</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1222,85 +1228,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="L7">
-        <v>0.4344569288389513</v>
+        <v>0.3718459495351925</v>
       </c>
       <c r="M7">
-        <v>2.23</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.04569672131147541</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.1922413793103448</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>2.23</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.04569672131147541</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.1922413793103448</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>0.477</v>
+        <v>14.6</v>
       </c>
       <c r="V7">
-        <v>0.009774590163934426</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="W7">
-        <v>0.1015761821366025</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="X7">
-        <v>0.05772058780846642</v>
+        <v>0.04826508986305431</v>
       </c>
       <c r="Y7">
-        <v>0.04385559432813604</v>
+        <v>0.06602062442265998</v>
       </c>
       <c r="Z7">
-        <v>0.07762530526805442</v>
+        <v>0.7078398195149463</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.02411719293771133</v>
+        <v>0.04817081295099274</v>
       </c>
       <c r="AC7">
-        <v>-0.02411719293771133</v>
+        <v>-0.04817081295099274</v>
       </c>
       <c r="AD7">
-        <v>277.6</v>
+        <v>0.347</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>277.6</v>
+        <v>0.347</v>
       </c>
       <c r="AG7">
-        <v>277.123</v>
+        <v>-14.253</v>
       </c>
       <c r="AH7">
-        <v>0.8504901960784313</v>
+        <v>0.01757228946169038</v>
       </c>
       <c r="AI7">
-        <v>0.6726435667555125</v>
+        <v>0.01539007406750344</v>
       </c>
       <c r="AJ7">
-        <v>0.8502713831180985</v>
+        <v>-2.769185933553527</v>
       </c>
       <c r="AK7">
-        <v>0.672264769311756</v>
+        <v>-1.79350698376746</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,124 +1320,496 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Bien Sparebank ASA (OB:BIEN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0591</v>
+      </c>
+      <c r="E8">
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>3.44</v>
+      </c>
+      <c r="L8">
+        <v>0.344689378757515</v>
+      </c>
+      <c r="M8">
+        <v>1.08</v>
+      </c>
+      <c r="N8">
+        <v>0.02037735849056604</v>
+      </c>
+      <c r="O8">
+        <v>0.313953488372093</v>
+      </c>
+      <c r="P8">
+        <v>1.08</v>
+      </c>
+      <c r="Q8">
+        <v>0.02037735849056604</v>
+      </c>
+      <c r="R8">
+        <v>0.313953488372093</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.159811320754717</v>
+      </c>
+      <c r="W8">
+        <v>0.0568595041322314</v>
+      </c>
+      <c r="X8">
+        <v>0.05849337205834117</v>
+      </c>
+      <c r="Y8">
+        <v>-0.001633867926109769</v>
+      </c>
+      <c r="Z8">
+        <v>0.05716314981556578</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05107705855990718</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05107705855990718</v>
+      </c>
+      <c r="AD8">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AG8">
+        <v>66.93000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.5872274143302181</v>
+      </c>
+      <c r="AI8">
+        <v>0.5890625</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5580755440673727</v>
+      </c>
+      <c r="AK8">
+        <v>0.5599431105161885</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>B2Holding ASA (OB:B2H)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.168</v>
-      </c>
-      <c r="E8">
-        <v>0.41</v>
-      </c>
-      <c r="F8">
-        <v>0.048</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>66</v>
-      </c>
-      <c r="L8">
-        <v>0.2378378378378379</v>
-      </c>
-      <c r="M8">
-        <v>6.920700000000001</v>
-      </c>
-      <c r="N8">
-        <v>0.01445728013369543</v>
-      </c>
-      <c r="O8">
-        <v>0.1048590909090909</v>
-      </c>
-      <c r="P8">
-        <v>6.920700000000001</v>
-      </c>
-      <c r="Q8">
-        <v>0.01445728013369543</v>
-      </c>
-      <c r="R8">
-        <v>0.1048590909090909</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>31.3</v>
-      </c>
-      <c r="V8">
-        <v>0.06538541884269898</v>
-      </c>
-      <c r="W8">
-        <v>0.1283297686175384</v>
-      </c>
-      <c r="X8">
-        <v>0.03701969376662254</v>
-      </c>
-      <c r="Y8">
-        <v>0.09131007485091588</v>
-      </c>
-      <c r="Z8">
-        <v>0.1639780180819004</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.03653649884976253</v>
-      </c>
-      <c r="AC8">
-        <v>-0.03653649884976253</v>
-      </c>
-      <c r="AD8">
-        <v>1102.4</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>1102.4</v>
-      </c>
-      <c r="AG8">
-        <v>1071.1</v>
-      </c>
-      <c r="AH8">
-        <v>0.6972361014483587</v>
-      </c>
-      <c r="AI8">
-        <v>0.6565812983919</v>
-      </c>
-      <c r="AJ8">
-        <v>0.691121435023874</v>
-      </c>
-      <c r="AK8">
-        <v>0.6500576561267221</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-0.229</v>
-      </c>
-      <c r="AQ8">
+      <c r="D9">
+        <v>0.114</v>
+      </c>
+      <c r="E9">
+        <v>-0.00817</v>
+      </c>
+      <c r="F9">
+        <v>0.544</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>35.4</v>
+      </c>
+      <c r="L9">
+        <v>0.1426844014510278</v>
+      </c>
+      <c r="M9">
+        <v>36.7</v>
+      </c>
+      <c r="N9">
+        <v>0.1188086759469084</v>
+      </c>
+      <c r="O9">
+        <v>1.036723163841808</v>
+      </c>
+      <c r="P9">
+        <v>21.1</v>
+      </c>
+      <c r="Q9">
+        <v>0.068306895435416</v>
+      </c>
+      <c r="R9">
+        <v>0.5960451977401131</v>
+      </c>
+      <c r="S9">
+        <v>15.6</v>
+      </c>
+      <c r="T9">
+        <v>0.4250681198910082</v>
+      </c>
+      <c r="U9">
+        <v>122.5</v>
+      </c>
+      <c r="V9">
+        <v>0.3965684687601166</v>
+      </c>
+      <c r="W9">
+        <v>0.0614050303555941</v>
+      </c>
+      <c r="X9">
+        <v>0.07085998110466979</v>
+      </c>
+      <c r="Y9">
+        <v>-0.009454950749075687</v>
+      </c>
+      <c r="Z9">
+        <v>0.1594677979174701</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06699299258698548</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06699299258698548</v>
+      </c>
+      <c r="AD9">
+        <v>964.1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>964.1</v>
+      </c>
+      <c r="AG9">
+        <v>841.6</v>
+      </c>
+      <c r="AH9">
+        <v>0.7573448546739985</v>
+      </c>
+      <c r="AI9">
+        <v>0.6688172043010753</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7315080399826163</v>
+      </c>
+      <c r="AK9">
+        <v>0.6380591357088704</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-0.368</v>
+      </c>
+      <c r="AQ9">
         <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huddlestock Fintech AS (OB:HUDL)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>-0.2032710280373832</v>
+      </c>
+      <c r="H10">
+        <v>-0.2107476635514019</v>
+      </c>
+      <c r="I10">
+        <v>-0.4462616822429906</v>
+      </c>
+      <c r="J10">
+        <v>-0.4462616822429906</v>
+      </c>
+      <c r="K10">
+        <v>-1.98</v>
+      </c>
+      <c r="L10">
+        <v>-0.4626168224299065</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>-0.1584</v>
+      </c>
+      <c r="X10">
+        <v>0.04839126808063351</v>
+      </c>
+      <c r="Y10">
+        <v>-0.2067912680806335</v>
+      </c>
+      <c r="Z10">
+        <v>0.5392465667128638</v>
+      </c>
+      <c r="AA10">
+        <v>-0.2406450800050396</v>
+      </c>
+      <c r="AB10">
+        <v>0.04820446627814727</v>
+      </c>
+      <c r="AC10">
+        <v>-0.2888495462831869</v>
+      </c>
+      <c r="AD10">
+        <v>1.06</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1.06</v>
+      </c>
+      <c r="AG10">
+        <v>1.06</v>
+      </c>
+      <c r="AH10">
+        <v>0.03401797175866496</v>
+      </c>
+      <c r="AI10">
+        <v>0.08242612752721618</v>
+      </c>
+      <c r="AJ10">
+        <v>0.03401797175866496</v>
+      </c>
+      <c r="AK10">
+        <v>0.08242612752721618</v>
+      </c>
+      <c r="AL10">
+        <v>0.153</v>
+      </c>
+      <c r="AM10">
+        <v>0.114</v>
+      </c>
+      <c r="AN10">
+        <v>-1.633281972265023</v>
+      </c>
+      <c r="AO10">
+        <v>-12.48366013071895</v>
+      </c>
+      <c r="AP10">
+        <v>-1.633281972265023</v>
+      </c>
+      <c r="AQ10">
+        <v>-16.75438596491228</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Norwegian Block Exchange AS (OB:NBX)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>-523.3333333333334</v>
+      </c>
+      <c r="H11">
+        <v>-523.3333333333334</v>
+      </c>
+      <c r="I11">
+        <v>-543.3333333333334</v>
+      </c>
+      <c r="J11">
+        <v>-543.3333333333334</v>
+      </c>
+      <c r="K11">
+        <v>-3.17</v>
+      </c>
+      <c r="L11">
+        <v>-352.2222222222222</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>3.53</v>
+      </c>
+      <c r="V11">
+        <v>0.346078431372549</v>
+      </c>
+      <c r="W11">
+        <v>-0.2935185185185185</v>
+      </c>
+      <c r="X11">
+        <v>0.04826477341772355</v>
+      </c>
+      <c r="Y11">
+        <v>-0.3417832919362421</v>
+      </c>
+      <c r="Z11">
+        <v>0.001095156972499391</v>
+      </c>
+      <c r="AA11">
+        <v>-0.595035288391336</v>
+      </c>
+      <c r="AB11">
+        <v>0.04817072711045851</v>
+      </c>
+      <c r="AC11">
+        <v>-0.6432060155017946</v>
+      </c>
+      <c r="AD11">
+        <v>0.182</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.182</v>
+      </c>
+      <c r="AG11">
+        <v>-3.348</v>
+      </c>
+      <c r="AH11">
+        <v>0.01753034097476401</v>
+      </c>
+      <c r="AI11">
+        <v>0.02224395013444146</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.4886164623467601</v>
+      </c>
+      <c r="AK11">
+        <v>-0.7196904557179707</v>
+      </c>
+      <c r="AL11">
+        <v>0.01</v>
+      </c>
+      <c r="AM11">
+        <v>0.01</v>
+      </c>
+      <c r="AN11">
+        <v>-0.03744855967078189</v>
+      </c>
+      <c r="AO11">
+        <v>-488.9999999999999</v>
+      </c>
+      <c r="AP11">
+        <v>0.6888888888888888</v>
+      </c>
+      <c r="AQ11">
+        <v>-488.9999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.114</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="E2">
-        <v>0.07205</v>
+        <v>-0.111</v>
       </c>
       <c r="F2">
-        <v>0.326</v>
+        <v>0.113</v>
       </c>
       <c r="G2">
-        <v>0.02768728746985437</v>
+        <v>0.2001620645398197</v>
       </c>
       <c r="H2">
-        <v>0.02762869003605574</v>
+        <v>0.1997383663965002</v>
       </c>
       <c r="I2">
-        <v>0.07031692055836032</v>
+        <v>0.2079475179233142</v>
       </c>
       <c r="J2">
-        <v>0.06250627467817614</v>
+        <v>0.1888939105149612</v>
       </c>
       <c r="K2">
-        <v>49.72</v>
+        <v>60.7</v>
       </c>
       <c r="L2">
-        <v>0.09104576276462693</v>
+        <v>0.1071603220812053</v>
       </c>
       <c r="M2">
-        <v>43.40051</v>
+        <v>19.92</v>
       </c>
       <c r="N2">
-        <v>0.06200072857142858</v>
+        <v>0.04352005592938914</v>
       </c>
       <c r="O2">
-        <v>0.872898431214803</v>
+        <v>0.328171334431631</v>
       </c>
       <c r="P2">
-        <v>27.80051</v>
+        <v>7.22</v>
       </c>
       <c r="Q2">
-        <v>0.03971501428571429</v>
+        <v>0.01577383553264004</v>
       </c>
       <c r="R2">
-        <v>0.5591413917940468</v>
+        <v>0.1189456342668863</v>
       </c>
       <c r="S2">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="T2">
-        <v>0.3594427807415166</v>
+        <v>0.6375502008032129</v>
       </c>
       <c r="U2">
-        <v>185.319</v>
+        <v>142.55</v>
       </c>
       <c r="V2">
-        <v>0.2647414285714286</v>
+        <v>0.3114349383902823</v>
       </c>
       <c r="W2">
-        <v>0.0614050303555941</v>
+        <v>0.02207207207207207</v>
       </c>
       <c r="X2">
-        <v>0.07085998110466979</v>
+        <v>0.05540682291581804</v>
       </c>
       <c r="Y2">
-        <v>-0.009454950749075687</v>
+        <v>-0.03333475084374597</v>
       </c>
       <c r="Z2">
-        <v>0.1419173244962068</v>
+        <v>0.2297339553762737</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04817081295099274</v>
+        <v>0.05002403621266956</v>
       </c>
       <c r="AC2">
-        <v>-0.04817081295099274</v>
+        <v>-0.06044606911189851</v>
       </c>
       <c r="AD2">
-        <v>2320.489</v>
+        <v>2004.778</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2320.489</v>
+        <v>2004.778</v>
       </c>
       <c r="AG2">
-        <v>2135.17</v>
+        <v>1862.228</v>
       </c>
       <c r="AH2">
-        <v>0.768249445702335</v>
+        <v>0.814123706902503</v>
       </c>
       <c r="AI2">
-        <v>0.653274453427265</v>
+        <v>0.6651071687581986</v>
       </c>
       <c r="AJ2">
-        <v>0.7531012249706367</v>
+        <v>0.8027024743658048</v>
       </c>
       <c r="AK2">
-        <v>0.6341894456704794</v>
+        <v>0.6484830419115302</v>
       </c>
       <c r="AL2">
-        <v>57.563</v>
+        <v>79.41800000000001</v>
       </c>
       <c r="AM2">
-        <v>56.998</v>
+        <v>77.51700000000001</v>
       </c>
       <c r="AN2">
-        <v>55.92752645151961</v>
+        <v>16.40974052549726</v>
       </c>
       <c r="AO2">
-        <v>0.6670951826694232</v>
+        <v>1.483165025560956</v>
       </c>
       <c r="AP2">
-        <v>51.46103974355885</v>
+        <v>15.24292379471229</v>
       </c>
       <c r="AQ2">
-        <v>0.6737078493982246</v>
+        <v>1.519537649805849</v>
       </c>
     </row>
     <row r="3">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.247</v>
+        <v>0.0852</v>
       </c>
       <c r="F3">
-        <v>0.108</v>
+        <v>0.029</v>
       </c>
       <c r="G3">
-        <v>0.09278350515463918</v>
+        <v>0.4462345447733234</v>
       </c>
       <c r="H3">
-        <v>0.09278350515463918</v>
+        <v>0.4462345447733234</v>
       </c>
       <c r="I3">
-        <v>0.2025997310623039</v>
+        <v>0.4739602847508431</v>
       </c>
       <c r="J3">
-        <v>0.2025997310623039</v>
+        <v>0.3638983776225092</v>
       </c>
       <c r="K3">
-        <v>-7.58</v>
+        <v>34.8</v>
       </c>
       <c r="L3">
-        <v>-0.03397579560735096</v>
+        <v>0.1303859123267141</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,7 +755,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,79 +764,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17.1</v>
+        <v>43.7</v>
       </c>
       <c r="V3">
-        <v>0.09484193011647254</v>
+        <v>0.2886393659180977</v>
       </c>
       <c r="W3">
-        <v>-0.0158477942713778</v>
+        <v>0.08691308691308691</v>
       </c>
       <c r="X3">
-        <v>0.08330100516502151</v>
+        <v>0.1077344653598947</v>
       </c>
       <c r="Y3">
-        <v>-0.0991487994363993</v>
+        <v>-0.02082137844680775</v>
       </c>
       <c r="Z3">
-        <v>0.1692716236722306</v>
+        <v>0.2235156184574156</v>
       </c>
       <c r="AA3">
-        <v>0.03429438543247345</v>
+        <v>0.08133697092994532</v>
       </c>
       <c r="AB3">
-        <v>0.07335195969104118</v>
+        <v>0.06476342953361329</v>
       </c>
       <c r="AC3">
-        <v>-0.03905757425856773</v>
+        <v>0.01657354139633203</v>
       </c>
       <c r="AD3">
-        <v>870.8</v>
+        <v>1020.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>870.8</v>
+        <v>1020.4</v>
       </c>
       <c r="AG3">
-        <v>853.6999999999999</v>
+        <v>976.6999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.8284654171819998</v>
+        <v>0.8707970643454515</v>
       </c>
       <c r="AI3">
-        <v>0.6869674976333229</v>
+        <v>0.698951983012535</v>
       </c>
       <c r="AJ3">
-        <v>0.8256286266924564</v>
+        <v>0.8657920397127914</v>
       </c>
       <c r="AK3">
-        <v>0.682686925229908</v>
+        <v>0.6896624770512639</v>
       </c>
       <c r="AL3">
-        <v>57.4</v>
+        <v>79.2</v>
       </c>
       <c r="AM3">
-        <v>57.242</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AN3">
-        <v>18.52765957446809</v>
+        <v>7.97810789679437</v>
       </c>
       <c r="AO3">
-        <v>0.7874564459930314</v>
+        <v>1.597222222222222</v>
       </c>
       <c r="AP3">
-        <v>18.16382978723404</v>
+        <v>7.636434714620797</v>
       </c>
       <c r="AQ3">
-        <v>0.7896299919639427</v>
+        <v>1.603295310519645</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhus Sparebank (OB:MELG)</t>
+          <t>mybank ASA (OTCNO:MYBANK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,12 +855,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0761</v>
-      </c>
-      <c r="E4">
-        <v>0.0698</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -874,85 +868,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>9.789999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="L4">
-        <v>0.4256521739130434</v>
+        <v>0.07668231611893583</v>
       </c>
       <c r="M4">
-        <v>2.68</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.05903083700440529</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2737487231869254</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>2.68</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.05903083700440529</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2737487231869254</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0.399</v>
+        <v>10.4</v>
       </c>
       <c r="V4">
-        <v>0.008788546255506608</v>
+        <v>0.6709677419354839</v>
       </c>
       <c r="W4">
-        <v>0.07246484085862324</v>
+        <v>0.02207207207207207</v>
       </c>
       <c r="X4">
-        <v>0.08309737866338221</v>
+        <v>0.04995464366293317</v>
       </c>
       <c r="Y4">
-        <v>-0.01063253780475897</v>
+        <v>-0.02788257159086109</v>
       </c>
       <c r="Z4">
-        <v>0.05579504297431244</v>
+        <v>0.8040770101925253</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04485768030112966</v>
+        <v>0.04982541651863501</v>
       </c>
       <c r="AC4">
-        <v>-0.04485768030112966</v>
+        <v>-0.04982541651863501</v>
       </c>
       <c r="AD4">
-        <v>218</v>
+        <v>0.248</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>218</v>
+        <v>0.248</v>
       </c>
       <c r="AG4">
-        <v>217.601</v>
+        <v>-10.152</v>
       </c>
       <c r="AH4">
-        <v>0.8276385725132879</v>
+        <v>0.01574803149606299</v>
       </c>
       <c r="AI4">
-        <v>0.654065406540654</v>
+        <v>0.009306514560192134</v>
       </c>
       <c r="AJ4">
-        <v>0.8273770822164175</v>
+        <v>-1.898279730740464</v>
       </c>
       <c r="AK4">
-        <v>0.6536507850682335</v>
+        <v>-0.6248153618906944</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Romsdal Sparebank (OB:ROMSB)</t>
+          <t>B2 Impact ASA (OB:B2I)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,6 +968,15 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.06480000000000001</v>
+      </c>
+      <c r="E5">
+        <v>-0.111</v>
+      </c>
+      <c r="F5">
+        <v>0.197</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -990,91 +990,94 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5.62</v>
+        <v>33.8</v>
       </c>
       <c r="L5">
-        <v>0.3469135802469136</v>
+        <v>0.1182645206438068</v>
       </c>
       <c r="M5">
-        <v>1.44452</v>
+        <v>19.92</v>
       </c>
       <c r="N5">
-        <v>0.05471666666666667</v>
+        <v>0.07455089820359281</v>
       </c>
       <c r="O5">
-        <v>0.2570320284697509</v>
+        <v>0.5893491124260355</v>
       </c>
       <c r="P5">
-        <v>1.44452</v>
+        <v>7.22</v>
       </c>
       <c r="Q5">
-        <v>0.05471666666666667</v>
+        <v>0.02702095808383233</v>
       </c>
       <c r="R5">
-        <v>0.2570320284697509</v>
+        <v>0.2136094674556213</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.6375502008032129</v>
       </c>
       <c r="U5">
-        <v>8.119999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V5">
-        <v>0.3075757575757576</v>
+        <v>0.3241017964071856</v>
       </c>
       <c r="W5">
-        <v>0.06162280701754386</v>
+        <v>0.07081500104755918</v>
       </c>
       <c r="X5">
-        <v>0.0759357472994194</v>
+        <v>0.08130261297622722</v>
       </c>
       <c r="Y5">
-        <v>-0.01431294028187555</v>
+        <v>-0.01048761192866804</v>
       </c>
       <c r="Z5">
-        <v>0.0786255096097845</v>
+        <v>0.2284389737031412</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04499700415648328</v>
+        <v>0.06044606911189851</v>
       </c>
       <c r="AC5">
-        <v>-0.04499700415648328</v>
+        <v>-0.06044606911189851</v>
       </c>
       <c r="AD5">
-        <v>100.8</v>
+        <v>979</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>100.8</v>
+        <v>979</v>
       </c>
       <c r="AG5">
-        <v>92.67999999999999</v>
+        <v>892.4</v>
       </c>
       <c r="AH5">
-        <v>0.7924528301886793</v>
+        <v>0.7855881880917991</v>
       </c>
       <c r="AI5">
-        <v>0.5656565656565656</v>
+        <v>0.651797603195739</v>
       </c>
       <c r="AJ5">
-        <v>0.7783003023177696</v>
+        <v>0.7695757157640566</v>
       </c>
       <c r="AK5">
-        <v>0.5449200376293509</v>
+        <v>0.6304931468136216</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-1.59</v>
+      </c>
+      <c r="AQ5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sunndal Sparebank (OB:SUNSB)</t>
+          <t>Norwegian Block Exchange AS (OB:NBX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,110 +1096,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.138</v>
-      </c>
-      <c r="E6">
-        <v>0.192</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>-22.25966850828729</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>-22.92817679558011</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>-16.57458563535912</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>-16.57458563535912</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>-2.64</v>
       </c>
       <c r="L6">
-        <v>0.3884892086330936</v>
+        <v>-14.58563535911602</v>
       </c>
       <c r="M6">
-        <v>1.49599</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.05688174904942966</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.2770351851851852</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.49599</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.05688174904942966</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2770351851851852</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>10.6</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
-        <v>0.403041825095057</v>
+        <v>0.4282407407407408</v>
       </c>
       <c r="W6">
-        <v>0.0849056603773585</v>
+        <v>-0.33</v>
       </c>
       <c r="X6">
-        <v>0.07299609103228802</v>
+        <v>0.05540682291581804</v>
       </c>
       <c r="Y6">
-        <v>0.01190956934507048</v>
+        <v>-0.3854068229158181</v>
       </c>
       <c r="Z6">
-        <v>0.08993038482440931</v>
+        <v>0.03890799656061908</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>-0.6448839208942388</v>
       </c>
       <c r="AB6">
-        <v>0.0450721653242823</v>
+        <v>0.05002403621266956</v>
       </c>
       <c r="AC6">
-        <v>-0.0450721653242823</v>
+        <v>-0.6949079571069084</v>
       </c>
       <c r="AD6">
-        <v>89.8</v>
+        <v>2.81</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>89.8</v>
+        <v>2.81</v>
       </c>
       <c r="AG6">
-        <v>79.2</v>
+        <v>0.96</v>
       </c>
       <c r="AH6">
-        <v>0.7734711455641688</v>
+        <v>0.394109396914446</v>
       </c>
       <c r="AI6">
-        <v>0.561601000625391</v>
+        <v>0.3721854304635761</v>
       </c>
       <c r="AJ6">
-        <v>0.7507109004739336</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AK6">
-        <v>0.5304755525787006</v>
+        <v>0.1684210526315789</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.077</v>
+      </c>
+      <c r="AN6">
+        <v>-0.9243421052631579</v>
+      </c>
+      <c r="AO6">
+        <v>-38.96103896103896</v>
+      </c>
+      <c r="AP6">
+        <v>-0.3157894736842105</v>
+      </c>
+      <c r="AQ6">
+        <v>-38.96103896103896</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mybank ASA (OTCNO:MYBANK)</t>
+          <t>Huddlestock Fintech AS (OB:HUDL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,22 +1222,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-0.2358437935843794</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.2524407252440725</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>-0.796373779637378</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>-0.796373779637378</v>
       </c>
       <c r="K7">
-        <v>2.8</v>
+        <v>-5.75</v>
       </c>
       <c r="L7">
-        <v>0.3718459495351925</v>
+        <v>-0.8019525801952581</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1240,7 +1246,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1249,567 +1255,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.7525773195876289</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.1142857142857143</v>
+        <v>-0.4872881355932203</v>
       </c>
       <c r="X7">
-        <v>0.04826508986305431</v>
+        <v>0.05085013585208177</v>
       </c>
       <c r="Y7">
-        <v>0.06602062442265998</v>
+        <v>-0.5381382714453021</v>
       </c>
       <c r="Z7">
-        <v>0.7078398195149463</v>
+        <v>0.9145408163265304</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.7283163265306121</v>
       </c>
       <c r="AB7">
-        <v>0.04817081295099274</v>
+        <v>0.04965008464131259</v>
       </c>
       <c r="AC7">
-        <v>-0.04817081295099274</v>
+        <v>-0.7779664111719247</v>
       </c>
       <c r="AD7">
-        <v>0.347</v>
+        <v>2.32</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.347</v>
+        <v>2.32</v>
       </c>
       <c r="AG7">
-        <v>-14.253</v>
+        <v>2.32</v>
       </c>
       <c r="AH7">
-        <v>0.01757228946169038</v>
+        <v>0.1073080481036078</v>
       </c>
       <c r="AI7">
-        <v>0.01539007406750344</v>
+        <v>0.1280353200883002</v>
       </c>
       <c r="AJ7">
-        <v>-2.769185933553527</v>
+        <v>0.1073080481036078</v>
       </c>
       <c r="AK7">
-        <v>-1.79350698376746</v>
+        <v>0.1280353200883002</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bien Sparebank ASA (OB:BIEN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0591</v>
-      </c>
-      <c r="E8">
-        <v>0.07429999999999999</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>3.44</v>
-      </c>
-      <c r="L8">
-        <v>0.344689378757515</v>
-      </c>
-      <c r="M8">
-        <v>1.08</v>
-      </c>
-      <c r="N8">
-        <v>0.02037735849056604</v>
-      </c>
-      <c r="O8">
-        <v>0.313953488372093</v>
-      </c>
-      <c r="P8">
-        <v>1.08</v>
-      </c>
-      <c r="Q8">
-        <v>0.02037735849056604</v>
-      </c>
-      <c r="R8">
-        <v>0.313953488372093</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="V8">
-        <v>0.159811320754717</v>
-      </c>
-      <c r="W8">
-        <v>0.0568595041322314</v>
-      </c>
-      <c r="X8">
-        <v>0.05849337205834117</v>
-      </c>
-      <c r="Y8">
-        <v>-0.001633867926109769</v>
-      </c>
-      <c r="Z8">
-        <v>0.05716314981556578</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.05107705855990718</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05107705855990718</v>
-      </c>
-      <c r="AD8">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="AG8">
-        <v>66.93000000000001</v>
-      </c>
-      <c r="AH8">
-        <v>0.5872274143302181</v>
-      </c>
-      <c r="AI8">
-        <v>0.5890625</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5580755440673727</v>
-      </c>
-      <c r="AK8">
-        <v>0.5599431105161885</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B2Holding ASA (OB:B2H)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.114</v>
-      </c>
-      <c r="E9">
-        <v>-0.00817</v>
-      </c>
-      <c r="F9">
-        <v>0.544</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>35.4</v>
-      </c>
-      <c r="L9">
-        <v>0.1426844014510278</v>
-      </c>
-      <c r="M9">
-        <v>36.7</v>
-      </c>
-      <c r="N9">
-        <v>0.1188086759469084</v>
-      </c>
-      <c r="O9">
-        <v>1.036723163841808</v>
-      </c>
-      <c r="P9">
-        <v>21.1</v>
-      </c>
-      <c r="Q9">
-        <v>0.068306895435416</v>
-      </c>
-      <c r="R9">
-        <v>0.5960451977401131</v>
-      </c>
-      <c r="S9">
-        <v>15.6</v>
-      </c>
-      <c r="T9">
-        <v>0.4250681198910082</v>
-      </c>
-      <c r="U9">
-        <v>122.5</v>
-      </c>
-      <c r="V9">
-        <v>0.3965684687601166</v>
-      </c>
-      <c r="W9">
-        <v>0.0614050303555941</v>
-      </c>
-      <c r="X9">
-        <v>0.07085998110466979</v>
-      </c>
-      <c r="Y9">
-        <v>-0.009454950749075687</v>
-      </c>
-      <c r="Z9">
-        <v>0.1594677979174701</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06699299258698548</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06699299258698548</v>
-      </c>
-      <c r="AD9">
-        <v>964.1</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>964.1</v>
-      </c>
-      <c r="AG9">
-        <v>841.6</v>
-      </c>
-      <c r="AH9">
-        <v>0.7573448546739985</v>
-      </c>
-      <c r="AI9">
-        <v>0.6688172043010753</v>
-      </c>
-      <c r="AJ9">
-        <v>0.7315080399826163</v>
-      </c>
-      <c r="AK9">
-        <v>0.6380591357088704</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-0.368</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Huddlestock Fintech AS (OB:HUDL)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>-0.2032710280373832</v>
-      </c>
-      <c r="H10">
-        <v>-0.2107476635514019</v>
-      </c>
-      <c r="I10">
-        <v>-0.4462616822429906</v>
-      </c>
-      <c r="J10">
-        <v>-0.4462616822429906</v>
-      </c>
-      <c r="K10">
-        <v>-1.98</v>
-      </c>
-      <c r="L10">
-        <v>-0.4626168224299065</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>-0.1584</v>
-      </c>
-      <c r="X10">
-        <v>0.04839126808063351</v>
-      </c>
-      <c r="Y10">
-        <v>-0.2067912680806335</v>
-      </c>
-      <c r="Z10">
-        <v>0.5392465667128638</v>
-      </c>
-      <c r="AA10">
-        <v>-0.2406450800050396</v>
-      </c>
-      <c r="AB10">
-        <v>0.04820446627814727</v>
-      </c>
-      <c r="AC10">
-        <v>-0.2888495462831869</v>
-      </c>
-      <c r="AD10">
-        <v>1.06</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>1.06</v>
-      </c>
-      <c r="AG10">
-        <v>1.06</v>
-      </c>
-      <c r="AH10">
-        <v>0.03401797175866496</v>
-      </c>
-      <c r="AI10">
-        <v>0.08242612752721618</v>
-      </c>
-      <c r="AJ10">
-        <v>0.03401797175866496</v>
-      </c>
-      <c r="AK10">
-        <v>0.08242612752721618</v>
-      </c>
-      <c r="AL10">
-        <v>0.153</v>
-      </c>
-      <c r="AM10">
-        <v>0.114</v>
-      </c>
-      <c r="AN10">
-        <v>-1.633281972265023</v>
-      </c>
-      <c r="AO10">
-        <v>-12.48366013071895</v>
-      </c>
-      <c r="AP10">
-        <v>-1.633281972265023</v>
-      </c>
-      <c r="AQ10">
-        <v>-16.75438596491228</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Norwegian Block Exchange AS (OB:NBX)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>-523.3333333333334</v>
-      </c>
-      <c r="H11">
-        <v>-523.3333333333334</v>
-      </c>
-      <c r="I11">
-        <v>-543.3333333333334</v>
-      </c>
-      <c r="J11">
-        <v>-543.3333333333334</v>
-      </c>
-      <c r="K11">
-        <v>-3.17</v>
-      </c>
-      <c r="L11">
-        <v>-352.2222222222222</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>3.53</v>
-      </c>
-      <c r="V11">
-        <v>0.346078431372549</v>
-      </c>
-      <c r="W11">
-        <v>-0.2935185185185185</v>
-      </c>
-      <c r="X11">
-        <v>0.04826477341772355</v>
-      </c>
-      <c r="Y11">
-        <v>-0.3417832919362421</v>
-      </c>
-      <c r="Z11">
-        <v>0.001095156972499391</v>
-      </c>
-      <c r="AA11">
-        <v>-0.595035288391336</v>
-      </c>
-      <c r="AB11">
-        <v>0.04817072711045851</v>
-      </c>
-      <c r="AC11">
-        <v>-0.6432060155017946</v>
-      </c>
-      <c r="AD11">
-        <v>0.182</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0.182</v>
-      </c>
-      <c r="AG11">
-        <v>-3.348</v>
-      </c>
-      <c r="AH11">
-        <v>0.01753034097476401</v>
-      </c>
-      <c r="AI11">
-        <v>0.02224395013444146</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.4886164623467601</v>
-      </c>
-      <c r="AK11">
-        <v>-0.7196904557179707</v>
-      </c>
-      <c r="AL11">
-        <v>0.01</v>
-      </c>
-      <c r="AM11">
-        <v>0.01</v>
-      </c>
-      <c r="AN11">
-        <v>-0.03744855967078189</v>
-      </c>
-      <c r="AO11">
-        <v>-488.9999999999999</v>
-      </c>
-      <c r="AP11">
-        <v>0.6888888888888888</v>
-      </c>
-      <c r="AQ11">
-        <v>-488.9999999999999</v>
+        <v>0.13</v>
+      </c>
+      <c r="AN7">
+        <v>-0.862453531598513</v>
+      </c>
+      <c r="AO7">
+        <v>-40.49645390070923</v>
+      </c>
+      <c r="AP7">
+        <v>-0.862453531598513</v>
+      </c>
+      <c r="AQ7">
+        <v>-43.92307692307693</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07500000000000001</v>
+        <v>0.02165</v>
       </c>
       <c r="E2">
-        <v>-0.111</v>
+        <v>0.04565</v>
       </c>
       <c r="F2">
-        <v>0.113</v>
+        <v>0.057</v>
       </c>
       <c r="G2">
-        <v>0.2001620645398197</v>
+        <v>0.2495888909190572</v>
       </c>
       <c r="H2">
-        <v>0.1997383663965002</v>
+        <v>0.2495888909190572</v>
       </c>
       <c r="I2">
-        <v>0.2079475179233142</v>
+        <v>0.220537182532432</v>
       </c>
       <c r="J2">
-        <v>0.1888939105149612</v>
+        <v>0.1806679042100423</v>
       </c>
       <c r="K2">
-        <v>60.7</v>
+        <v>44.7</v>
       </c>
       <c r="L2">
-        <v>0.1071603220812053</v>
+        <v>0.08167367074730496</v>
       </c>
       <c r="M2">
-        <v>19.92</v>
+        <v>27.25</v>
       </c>
       <c r="N2">
-        <v>0.04352005592938914</v>
+        <v>0.06420829406220548</v>
       </c>
       <c r="O2">
-        <v>0.328171334431631</v>
+        <v>0.6096196868008948</v>
       </c>
       <c r="P2">
-        <v>7.22</v>
+        <v>24.5</v>
       </c>
       <c r="Q2">
-        <v>0.01577383553264004</v>
+        <v>0.05772855796418473</v>
       </c>
       <c r="R2">
-        <v>0.1189456342668863</v>
+        <v>0.5480984340044742</v>
       </c>
       <c r="S2">
-        <v>12.7</v>
+        <v>2.75</v>
       </c>
       <c r="T2">
-        <v>0.6375502008032129</v>
+        <v>0.1009174311926606</v>
       </c>
       <c r="U2">
-        <v>142.55</v>
+        <v>77.5</v>
       </c>
       <c r="V2">
-        <v>0.3114349383902823</v>
+        <v>0.1826107445805844</v>
       </c>
       <c r="W2">
-        <v>0.02207207207207207</v>
+        <v>0.04495266525741366</v>
       </c>
       <c r="X2">
-        <v>0.05540682291581804</v>
+        <v>0.1120440578583078</v>
       </c>
       <c r="Y2">
-        <v>-0.03333475084374597</v>
+        <v>-0.06709139260089415</v>
       </c>
       <c r="Z2">
-        <v>0.2297339553762737</v>
+        <v>0.2017844633705711</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.03818574668452862</v>
       </c>
       <c r="AB2">
-        <v>0.05002403621266956</v>
+        <v>0.06813808756150709</v>
       </c>
       <c r="AC2">
-        <v>-0.06044606911189851</v>
+        <v>-0.02995234087697847</v>
       </c>
       <c r="AD2">
-        <v>2004.778</v>
+        <v>1986.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2004.778</v>
+        <v>1986.9</v>
       </c>
       <c r="AG2">
-        <v>1862.228</v>
+        <v>1909.4</v>
       </c>
       <c r="AH2">
-        <v>0.814123706902503</v>
+        <v>0.8239953552025878</v>
       </c>
       <c r="AI2">
-        <v>0.6651071687581986</v>
+        <v>0.6615942994139585</v>
       </c>
       <c r="AJ2">
-        <v>0.8027024743658048</v>
+        <v>0.818150655583169</v>
       </c>
       <c r="AK2">
-        <v>0.6484830419115302</v>
+        <v>0.6526301397956046</v>
       </c>
       <c r="AL2">
-        <v>79.41800000000001</v>
+        <v>100.6</v>
       </c>
       <c r="AM2">
-        <v>77.51700000000001</v>
+        <v>97.256</v>
       </c>
       <c r="AN2">
-        <v>16.40974052549726</v>
+        <v>16.3665568369028</v>
       </c>
       <c r="AO2">
-        <v>1.483165025560956</v>
+        <v>1.199801192842942</v>
       </c>
       <c r="AP2">
-        <v>15.24292379471229</v>
+        <v>15.72817133443163</v>
       </c>
       <c r="AQ2">
-        <v>1.519537649805849</v>
+        <v>1.24105453648104</v>
       </c>
     </row>
     <row r="3">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0852</v>
-      </c>
-      <c r="F3">
-        <v>0.029</v>
+        <v>-0.0358</v>
+      </c>
+      <c r="E3">
+        <v>-0.0407</v>
       </c>
       <c r="G3">
-        <v>0.4462345447733234</v>
+        <v>0.5278207109737248</v>
       </c>
       <c r="H3">
-        <v>0.4462345447733234</v>
+        <v>0.5278207109737248</v>
       </c>
       <c r="I3">
-        <v>0.4739602847508431</v>
+        <v>0.4663833075734157</v>
       </c>
       <c r="J3">
-        <v>0.3638983776225092</v>
+        <v>0.4020126948093766</v>
       </c>
       <c r="K3">
-        <v>34.8</v>
+        <v>14</v>
       </c>
       <c r="L3">
-        <v>0.1303859123267141</v>
+        <v>0.05409582689335394</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>43.7</v>
+        <v>27.6</v>
       </c>
       <c r="V3">
-        <v>0.2886393659180977</v>
+        <v>0.2813455657492355</v>
       </c>
       <c r="W3">
-        <v>0.08691308691308691</v>
+        <v>0.03119429590017825</v>
       </c>
       <c r="X3">
-        <v>0.1077344653598947</v>
+        <v>0.145468995826725</v>
       </c>
       <c r="Y3">
-        <v>-0.02082137844680775</v>
+        <v>-0.1142746999265468</v>
       </c>
       <c r="Z3">
-        <v>0.2235156184574156</v>
+        <v>0.1899728400499156</v>
       </c>
       <c r="AA3">
-        <v>0.08133697092994532</v>
+        <v>0.07637149336905724</v>
       </c>
       <c r="AB3">
-        <v>0.06476342953361329</v>
+        <v>0.07645594212539331</v>
       </c>
       <c r="AC3">
-        <v>0.01657354139633203</v>
+        <v>-8.444875633606408E-05</v>
       </c>
       <c r="AD3">
-        <v>1020.4</v>
+        <v>1082.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1020.4</v>
+        <v>1082.2</v>
       </c>
       <c r="AG3">
-        <v>976.6999999999999</v>
+        <v>1054.6</v>
       </c>
       <c r="AH3">
-        <v>0.8707970643454515</v>
+        <v>0.9168855375751929</v>
       </c>
       <c r="AI3">
-        <v>0.698951983012535</v>
+        <v>0.6990052964733239</v>
       </c>
       <c r="AJ3">
-        <v>0.8657920397127914</v>
+        <v>0.9148954628264077</v>
       </c>
       <c r="AK3">
-        <v>0.6896624770512639</v>
+        <v>0.693542022885703</v>
       </c>
       <c r="AL3">
-        <v>79.2</v>
+        <v>100.6</v>
       </c>
       <c r="AM3">
-        <v>78.90000000000001</v>
+        <v>100.196</v>
       </c>
       <c r="AN3">
-        <v>7.97810789679437</v>
+        <v>8.914332784184515</v>
       </c>
       <c r="AO3">
-        <v>1.597222222222222</v>
+        <v>1.199801192842942</v>
       </c>
       <c r="AP3">
-        <v>7.636434714620797</v>
+        <v>8.686985172981879</v>
       </c>
       <c r="AQ3">
-        <v>1.603295310519645</v>
+        <v>1.204638907740828</v>
       </c>
     </row>
     <row r="4">
@@ -847,13 +847,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mybank ASA (OTCNO:MYBANK)</t>
+          <t>B2 Impact ASA (OB:B2I)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
+      </c>
+      <c r="D4">
+        <v>0.0791</v>
+      </c>
+      <c r="E4">
+        <v>0.132</v>
+      </c>
+      <c r="F4">
+        <v>0.057</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -868,466 +877,94 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.49</v>
+        <v>30.7</v>
       </c>
       <c r="L4">
-        <v>0.07668231611893583</v>
+        <v>0.1064124783362218</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>27.25</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08351210542445602</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.8876221498371336</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>24.5</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.07508427827152926</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.7980456026058632</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="T4">
+        <v>0.1009174311926606</v>
       </c>
       <c r="U4">
-        <v>10.4</v>
+        <v>49.9</v>
       </c>
       <c r="V4">
-        <v>0.6709677419354839</v>
+        <v>0.15292675452038</v>
       </c>
       <c r="W4">
-        <v>0.02207207207207207</v>
+        <v>0.05871103461464908</v>
       </c>
       <c r="X4">
-        <v>0.04995464366293317</v>
+        <v>0.07861911988989059</v>
       </c>
       <c r="Y4">
-        <v>-0.02788257159086109</v>
+        <v>-0.01990808527524152</v>
       </c>
       <c r="Z4">
-        <v>0.8040770101925253</v>
+        <v>0.2137037037037037</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04982541651863501</v>
+        <v>0.05982023299762088</v>
       </c>
       <c r="AC4">
-        <v>-0.04982541651863501</v>
+        <v>-0.05982023299762088</v>
       </c>
       <c r="AD4">
-        <v>0.248</v>
+        <v>904.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.248</v>
+        <v>904.7</v>
       </c>
       <c r="AG4">
-        <v>-10.152</v>
+        <v>854.8000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.01574803149606299</v>
+        <v>0.7349309504467912</v>
       </c>
       <c r="AI4">
-        <v>0.009306514560192134</v>
+        <v>0.6217869415807561</v>
       </c>
       <c r="AJ4">
-        <v>-1.898279730740464</v>
+        <v>0.7237321141308949</v>
       </c>
       <c r="AK4">
-        <v>-0.6248153618906944</v>
+        <v>0.6083552772044695</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>B2 Impact ASA (OB:B2I)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.06480000000000001</v>
-      </c>
-      <c r="E5">
-        <v>-0.111</v>
-      </c>
-      <c r="F5">
-        <v>0.197</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>33.8</v>
-      </c>
-      <c r="L5">
-        <v>0.1182645206438068</v>
-      </c>
-      <c r="M5">
-        <v>19.92</v>
-      </c>
-      <c r="N5">
-        <v>0.07455089820359281</v>
-      </c>
-      <c r="O5">
-        <v>0.5893491124260355</v>
-      </c>
-      <c r="P5">
-        <v>7.22</v>
-      </c>
-      <c r="Q5">
-        <v>0.02702095808383233</v>
-      </c>
-      <c r="R5">
-        <v>0.2136094674556213</v>
-      </c>
-      <c r="S5">
-        <v>12.7</v>
-      </c>
-      <c r="T5">
-        <v>0.6375502008032129</v>
-      </c>
-      <c r="U5">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="V5">
-        <v>0.3241017964071856</v>
-      </c>
-      <c r="W5">
-        <v>0.07081500104755918</v>
-      </c>
-      <c r="X5">
-        <v>0.08130261297622722</v>
-      </c>
-      <c r="Y5">
-        <v>-0.01048761192866804</v>
-      </c>
-      <c r="Z5">
-        <v>0.2284389737031412</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06044606911189851</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06044606911189851</v>
-      </c>
-      <c r="AD5">
-        <v>979</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>979</v>
-      </c>
-      <c r="AG5">
-        <v>892.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.7855881880917991</v>
-      </c>
-      <c r="AI5">
-        <v>0.651797603195739</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7695757157640566</v>
-      </c>
-      <c r="AK5">
-        <v>0.6304931468136216</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-1.59</v>
-      </c>
-      <c r="AQ5">
+        <v>-2.94</v>
+      </c>
+      <c r="AQ4">
         <v>-0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Norwegian Block Exchange AS (OB:NBX)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>-22.25966850828729</v>
-      </c>
-      <c r="H6">
-        <v>-22.92817679558011</v>
-      </c>
-      <c r="I6">
-        <v>-16.57458563535912</v>
-      </c>
-      <c r="J6">
-        <v>-16.57458563535912</v>
-      </c>
-      <c r="K6">
-        <v>-2.64</v>
-      </c>
-      <c r="L6">
-        <v>-14.58563535911602</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1.85</v>
-      </c>
-      <c r="V6">
-        <v>0.4282407407407408</v>
-      </c>
-      <c r="W6">
-        <v>-0.33</v>
-      </c>
-      <c r="X6">
-        <v>0.05540682291581804</v>
-      </c>
-      <c r="Y6">
-        <v>-0.3854068229158181</v>
-      </c>
-      <c r="Z6">
-        <v>0.03890799656061908</v>
-      </c>
-      <c r="AA6">
-        <v>-0.6448839208942388</v>
-      </c>
-      <c r="AB6">
-        <v>0.05002403621266956</v>
-      </c>
-      <c r="AC6">
-        <v>-0.6949079571069084</v>
-      </c>
-      <c r="AD6">
-        <v>2.81</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>2.81</v>
-      </c>
-      <c r="AG6">
-        <v>0.96</v>
-      </c>
-      <c r="AH6">
-        <v>0.394109396914446</v>
-      </c>
-      <c r="AI6">
-        <v>0.3721854304635761</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AK6">
-        <v>0.1684210526315789</v>
-      </c>
-      <c r="AL6">
-        <v>0.077</v>
-      </c>
-      <c r="AM6">
-        <v>0.077</v>
-      </c>
-      <c r="AN6">
-        <v>-0.9243421052631579</v>
-      </c>
-      <c r="AO6">
-        <v>-38.96103896103896</v>
-      </c>
-      <c r="AP6">
-        <v>-0.3157894736842105</v>
-      </c>
-      <c r="AQ6">
-        <v>-38.96103896103896</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Huddlestock Fintech AS (OB:HUDL)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>-0.2358437935843794</v>
-      </c>
-      <c r="H7">
-        <v>-0.2524407252440725</v>
-      </c>
-      <c r="I7">
-        <v>-0.796373779637378</v>
-      </c>
-      <c r="J7">
-        <v>-0.796373779637378</v>
-      </c>
-      <c r="K7">
-        <v>-5.75</v>
-      </c>
-      <c r="L7">
-        <v>-0.8019525801952581</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>-0.4872881355932203</v>
-      </c>
-      <c r="X7">
-        <v>0.05085013585208177</v>
-      </c>
-      <c r="Y7">
-        <v>-0.5381382714453021</v>
-      </c>
-      <c r="Z7">
-        <v>0.9145408163265304</v>
-      </c>
-      <c r="AA7">
-        <v>-0.7283163265306121</v>
-      </c>
-      <c r="AB7">
-        <v>0.04965008464131259</v>
-      </c>
-      <c r="AC7">
-        <v>-0.7779664111719247</v>
-      </c>
-      <c r="AD7">
-        <v>2.32</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>2.32</v>
-      </c>
-      <c r="AG7">
-        <v>2.32</v>
-      </c>
-      <c r="AH7">
-        <v>0.1073080481036078</v>
-      </c>
-      <c r="AI7">
-        <v>0.1280353200883002</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1073080481036078</v>
-      </c>
-      <c r="AK7">
-        <v>0.1280353200883002</v>
-      </c>
-      <c r="AL7">
-        <v>0.141</v>
-      </c>
-      <c r="AM7">
-        <v>0.13</v>
-      </c>
-      <c r="AN7">
-        <v>-0.862453531598513</v>
-      </c>
-      <c r="AO7">
-        <v>-40.49645390070923</v>
-      </c>
-      <c r="AP7">
-        <v>-0.862453531598513</v>
-      </c>
-      <c r="AQ7">
-        <v>-43.92307692307693</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -597,40 +597,40 @@
         <v>0.057</v>
       </c>
       <c r="G2">
-        <v>0.2495888909190572</v>
+        <v>0.2410356663453482</v>
       </c>
       <c r="H2">
-        <v>0.2495888909190572</v>
+        <v>0.2346104990045135</v>
       </c>
       <c r="I2">
-        <v>0.220537182532432</v>
+        <v>0.1968450734678066</v>
       </c>
       <c r="J2">
-        <v>0.1806679042100423</v>
+        <v>0.1790519944723291</v>
       </c>
       <c r="K2">
-        <v>44.7</v>
+        <v>33.11</v>
       </c>
       <c r="L2">
-        <v>0.08167367074730496</v>
+        <v>0.05965712020612427</v>
       </c>
       <c r="M2">
         <v>27.25</v>
       </c>
       <c r="N2">
-        <v>0.06420829406220548</v>
+        <v>0.06218337821185706</v>
       </c>
       <c r="O2">
-        <v>0.6096196868008948</v>
+        <v>0.8230141951072184</v>
       </c>
       <c r="P2">
         <v>24.5</v>
       </c>
       <c r="Q2">
-        <v>0.05772855796418473</v>
+        <v>0.05590799141983478</v>
       </c>
       <c r="R2">
-        <v>0.5480984340044742</v>
+        <v>0.7399577167019028</v>
       </c>
       <c r="S2">
         <v>2.75</v>
@@ -639,73 +639,73 @@
         <v>0.1009174311926606</v>
       </c>
       <c r="U2">
-        <v>77.5</v>
+        <v>77.589</v>
       </c>
       <c r="V2">
-        <v>0.1826107445805844</v>
+        <v>0.1770549039295331</v>
       </c>
       <c r="W2">
-        <v>0.04495266525741366</v>
+        <v>-0.196428168505607</v>
       </c>
       <c r="X2">
-        <v>0.1120440578583078</v>
+        <v>0.06922513387058075</v>
       </c>
       <c r="Y2">
-        <v>-0.06709139260089415</v>
+        <v>-0.2656533023761878</v>
       </c>
       <c r="Z2">
-        <v>0.2017844633705711</v>
+        <v>0.2037014607648829</v>
       </c>
       <c r="AA2">
-        <v>0.03818574668452862</v>
+        <v>-0.2175438596491228</v>
       </c>
       <c r="AB2">
-        <v>0.06813808756150709</v>
+        <v>0.05971954997436803</v>
       </c>
       <c r="AC2">
-        <v>-0.02995234087697847</v>
+        <v>-0.2772634096234908</v>
       </c>
       <c r="AD2">
-        <v>1986.9</v>
+        <v>1991.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1986.9</v>
+        <v>1991.6</v>
       </c>
       <c r="AG2">
-        <v>1909.4</v>
+        <v>1914.011</v>
       </c>
       <c r="AH2">
-        <v>0.8239953552025878</v>
+        <v>0.8196491921212271</v>
       </c>
       <c r="AI2">
-        <v>0.6615942994139585</v>
+        <v>0.6581647659113217</v>
       </c>
       <c r="AJ2">
-        <v>0.818150655583169</v>
+        <v>0.8137002700840181</v>
       </c>
       <c r="AK2">
-        <v>0.6526301397956046</v>
+        <v>0.6491691598259532</v>
       </c>
       <c r="AL2">
-        <v>100.6</v>
+        <v>101.174</v>
       </c>
       <c r="AM2">
-        <v>97.256</v>
+        <v>97.75599999999999</v>
       </c>
       <c r="AN2">
-        <v>16.3665568369028</v>
+        <v>17.33182490644852</v>
       </c>
       <c r="AO2">
-        <v>1.199801192842942</v>
+        <v>1.079822879395892</v>
       </c>
       <c r="AP2">
-        <v>15.72817133443163</v>
+        <v>16.6566095204943</v>
       </c>
       <c r="AQ2">
-        <v>1.24105453648104</v>
+        <v>1.117578460657147</v>
       </c>
     </row>
     <row r="3">
@@ -779,10 +779,10 @@
         <v>0.03119429590017825</v>
       </c>
       <c r="X3">
-        <v>0.145468995826725</v>
+        <v>0.1454049175240318</v>
       </c>
       <c r="Y3">
-        <v>-0.1142746999265468</v>
+        <v>-0.1142106216238536</v>
       </c>
       <c r="Z3">
         <v>0.1899728400499156</v>
@@ -791,10 +791,10 @@
         <v>0.07637149336905724</v>
       </c>
       <c r="AB3">
-        <v>0.07645594212539331</v>
+        <v>0.07645061629171186</v>
       </c>
       <c r="AC3">
-        <v>-8.444875633606408E-05</v>
+        <v>-7.912292265462029E-05</v>
       </c>
       <c r="AD3">
         <v>1082.2</v>
@@ -916,10 +916,10 @@
         <v>0.05871103461464908</v>
       </c>
       <c r="X4">
-        <v>0.07861911988989059</v>
+        <v>0.07859802011376676</v>
       </c>
       <c r="Y4">
-        <v>-0.01990808527524152</v>
+        <v>-0.01988698549911769</v>
       </c>
       <c r="Z4">
         <v>0.2137037037037037</v>
@@ -928,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05982023299762088</v>
+        <v>0.05981464010001795</v>
       </c>
       <c r="AC4">
-        <v>-0.05982023299762088</v>
+        <v>-0.05981464010001795</v>
       </c>
       <c r="AD4">
         <v>904.7</v>
@@ -965,6 +965,256 @@
       </c>
       <c r="AQ4">
         <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Norwegian Block Exchange AS (OB:NBX)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-6.778082191780822</v>
+      </c>
+      <c r="H5">
+        <v>-7.780821917808219</v>
+      </c>
+      <c r="I5">
+        <v>-6.794520547945206</v>
+      </c>
+      <c r="J5">
+        <v>-6.794520547945206</v>
+      </c>
+      <c r="K5">
+        <v>-2.01</v>
+      </c>
+      <c r="L5">
+        <v>-5.506849315068493</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.089</v>
+      </c>
+      <c r="V5">
+        <v>0.01995515695067265</v>
+      </c>
+      <c r="W5">
+        <v>-0.4240506329113923</v>
+      </c>
+      <c r="X5">
+        <v>0.05985224762739474</v>
+      </c>
+      <c r="Y5">
+        <v>-0.4839028805387871</v>
+      </c>
+      <c r="Z5">
+        <v>0.06403508771929824</v>
+      </c>
+      <c r="AA5">
+        <v>-0.4350877192982455</v>
+      </c>
+      <c r="AB5">
+        <v>0.05962445984871811</v>
+      </c>
+      <c r="AC5">
+        <v>-0.4947121791469636</v>
+      </c>
+      <c r="AD5">
+        <v>2.03</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.03</v>
+      </c>
+      <c r="AG5">
+        <v>1.941</v>
+      </c>
+      <c r="AH5">
+        <v>0.312788906009245</v>
+      </c>
+      <c r="AI5">
+        <v>0.2327981651376146</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3032338697078582</v>
+      </c>
+      <c r="AK5">
+        <v>0.2248870351060132</v>
+      </c>
+      <c r="AL5">
+        <v>0.244</v>
+      </c>
+      <c r="AM5">
+        <v>0.244</v>
+      </c>
+      <c r="AN5">
+        <v>-0.7718631178707224</v>
+      </c>
+      <c r="AO5">
+        <v>-10.16393442622951</v>
+      </c>
+      <c r="AP5">
+        <v>-0.7380228136882129</v>
+      </c>
+      <c r="AQ5">
+        <v>-10.16393442622951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Huddlestock Fintech AS (OB:HUDL)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>-0.04768392370572203</v>
+      </c>
+      <c r="H6">
+        <v>-0.4836512261580381</v>
+      </c>
+      <c r="I6">
+        <v>-1.222070844686649</v>
+      </c>
+      <c r="J6">
+        <v>-1.222070844686649</v>
+      </c>
+      <c r="K6">
+        <v>-9.58</v>
+      </c>
+      <c r="L6">
+        <v>-1.305177111716621</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>-0.5474285714285715</v>
+      </c>
+      <c r="X6">
+        <v>0.05847792506721807</v>
+      </c>
+      <c r="Y6">
+        <v>-0.6059064964957895</v>
+      </c>
+      <c r="Z6">
+        <v>1.112121212121212</v>
+      </c>
+      <c r="AA6">
+        <v>-1</v>
+      </c>
+      <c r="AB6">
+        <v>0.05507241551364598</v>
+      </c>
+      <c r="AC6">
+        <v>-1.055072415513646</v>
+      </c>
+      <c r="AD6">
+        <v>2.67</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2.67</v>
+      </c>
+      <c r="AG6">
+        <v>2.67</v>
+      </c>
+      <c r="AH6">
+        <v>0.2219451371571072</v>
+      </c>
+      <c r="AI6">
+        <v>0.1897654584221748</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2219451371571072</v>
+      </c>
+      <c r="AK6">
+        <v>0.1897654584221748</v>
+      </c>
+      <c r="AL6">
+        <v>0.33</v>
+      </c>
+      <c r="AM6">
+        <v>0.256</v>
+      </c>
+      <c r="AN6">
+        <v>-0.6917098445595855</v>
+      </c>
+      <c r="AO6">
+        <v>-27.18181818181818</v>
+      </c>
+      <c r="AP6">
+        <v>-0.6917098445595855</v>
+      </c>
+      <c r="AQ6">
+        <v>-35.0390625</v>
       </c>
     </row>
   </sheetData>
